--- a/TME 2-1/Regular Assessment TME 2-1.xlsx
+++ b/TME 2-1/Regular Assessment TME 2-1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Attendance\TME 2-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA60914-6C22-40BC-88A2-AF86FC5C2BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61057FDA-AE48-4E10-B454-2FF641071EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TME 2-1 Attendance" sheetId="2" r:id="rId1"/>

--- a/TME 2-1/Regular Assessment TME 2-1.xlsx
+++ b/TME 2-1/Regular Assessment TME 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61057FDA-AE48-4E10-B454-2FF641071EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197119FF-96DB-4268-92A1-0AE65DA810F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="45">
   <si>
     <t>SL</t>
   </si>
@@ -643,7 +643,8 @@
     <col min="6" max="6" width="34.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="24" width="25.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="24" width="25.77734375" style="2" customWidth="1"/>
     <col min="25" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -793,7 +794,9 @@
       <c r="I3" s="4">
         <v>46267</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="4">
+        <v>46271</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -821,7 +824,7 @@
       </c>
       <c r="D4" s="11">
         <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>32</v>
@@ -838,7 +841,9 @@
       <c r="I4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -884,7 +889,9 @@
       <c r="I5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -930,7 +937,9 @@
       <c r="I6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -976,7 +985,9 @@
       <c r="I7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1022,7 +1033,9 @@
       <c r="I8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1051,7 +1064,7 @@
       </c>
       <c r="D9" s="11">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>32</v>
@@ -1068,7 +1081,9 @@
       <c r="I9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1097,7 +1112,7 @@
       </c>
       <c r="D10" s="11">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>31</v>
@@ -1114,7 +1129,9 @@
       <c r="I10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="1"/>
+      <c r="J10" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1143,7 +1160,7 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>32</v>
@@ -1160,7 +1177,9 @@
       <c r="I11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1189,7 +1208,7 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>32</v>
@@ -1206,7 +1225,9 @@
       <c r="I12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="J12" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1252,7 +1273,9 @@
       <c r="I13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1281,7 +1304,7 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>32</v>
@@ -1298,7 +1321,9 @@
       <c r="I14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1327,7 +1352,7 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>31</v>
@@ -1344,7 +1369,9 @@
       <c r="I15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1390,7 +1417,9 @@
       <c r="I16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1419,7 +1448,7 @@
       </c>
       <c r="D17" s="11">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>32</v>
@@ -1436,7 +1465,9 @@
       <c r="I17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="1"/>
+      <c r="J17" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -1465,7 +1496,7 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>32</v>
@@ -1482,7 +1513,9 @@
       <c r="I18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="1"/>
+      <c r="J18" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1511,7 +1544,7 @@
       </c>
       <c r="D19" s="11">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>31</v>
@@ -1528,7 +1561,9 @@
       <c r="I19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1574,7 +1609,9 @@
       <c r="I20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1620,7 +1657,9 @@
       <c r="I21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1666,7 +1705,9 @@
       <c r="I22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1712,7 +1753,9 @@
       <c r="I23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1741,7 +1784,7 @@
       </c>
       <c r="D24" s="11">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>32</v>
@@ -1758,7 +1801,9 @@
       <c r="I24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -1804,7 +1849,9 @@
       <c r="I25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J25" s="1"/>
+      <c r="J25" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -1833,7 +1880,7 @@
       </c>
       <c r="D26" s="11">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>31</v>
@@ -1850,7 +1897,9 @@
       <c r="I26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J26" s="1"/>
+      <c r="J26" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -1879,7 +1928,7 @@
       </c>
       <c r="D27" s="11">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>32</v>
@@ -1896,7 +1945,9 @@
       <c r="I27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -1925,7 +1976,7 @@
       </c>
       <c r="D28" s="11">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>31</v>
@@ -1942,7 +1993,9 @@
       <c r="I28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J28" s="1"/>
+      <c r="J28" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -1971,7 +2024,7 @@
       </c>
       <c r="D29" s="11">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>31</v>
@@ -1988,7 +2041,9 @@
       <c r="I29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2034,7 +2089,9 @@
       <c r="I30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2063,7 +2120,7 @@
       </c>
       <c r="D31" s="11">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>31</v>
@@ -2080,7 +2137,9 @@
       <c r="I31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J31" s="1"/>
+      <c r="J31" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>

--- a/TME 2-1/Regular Assessment TME 2-1.xlsx
+++ b/TME 2-1/Regular Assessment TME 2-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197119FF-96DB-4268-92A1-0AE65DA810F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C38B05B-FC23-4903-97BF-F6A9D03FF6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TME 2-1 Attendance" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="53">
   <si>
     <t>SL</t>
   </si>
@@ -167,13 +167,37 @@
     <t>Assignment 3</t>
   </si>
   <si>
-    <t>Assignmnet 4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>Not Clear</t>
+  </si>
+  <si>
+    <t>Drew 3 Figures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underlapping, Yarn Feeding, Pressing Mistakes </t>
+  </si>
+  <si>
+    <t>Drew 2 Figures &amp; SJCKM</t>
+  </si>
+  <si>
+    <t>Drew 3 Figures &amp; SJCKM</t>
+  </si>
+  <si>
+    <t>Drew 3 Figures, Knock Over Missing, Pressing Mistake</t>
+  </si>
+  <si>
+    <t>Comments on Assignment 1</t>
+  </si>
+  <si>
+    <t>Assignment 4</t>
+  </si>
+  <si>
+    <t>Comments on Assignment 2</t>
   </si>
 </sst>
 </file>
@@ -218,7 +242,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,6 +278,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -283,7 +319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -318,16 +354,22 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -649,10 +691,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="15"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
@@ -2175,7 +2217,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A66B3EF-818E-4A70-9374-2DAEC6B795EE}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.21875" style="2" bestFit="1" customWidth="1"/>
@@ -2183,16 +2225,17 @@
     <col min="3" max="3" width="39.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="12.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" style="2" customWidth="1"/>
+    <col min="10" max="11" width="52.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="15"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
@@ -2206,14 +2249,20 @@
         <v>41</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" s="15"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I1" s="16"/>
+      <c r="J1" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -2230,10 +2279,12 @@
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-    </row>
-    <row r="3" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+    </row>
+    <row r="3" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2243,26 +2294,28 @@
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="13">
-        <v>20</v>
-      </c>
-      <c r="I3" s="13">
+      <c r="H3" s="3">
+        <v>30</v>
+      </c>
+      <c r="I3" s="12">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2272,20 +2325,24 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="1">
+        <v>7.5</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1">
         <f>SUM(D4:G4)</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I4" s="1">
-        <f>(H4/20)*7.5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <f>(H4/30)*7.5</f>
+        <v>1.875</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A31" si="0">A4+1</f>
         <v>2</v>
@@ -2296,20 +2353,24 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1">
+        <v>7.5</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1">
         <f t="shared" ref="H5:H31" si="1">SUM(D5:G5)</f>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" ref="I5:I31" si="2">(H5/20)*7.5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" ref="I5:I31" si="2">(H5/30)*7.5</f>
+        <v>1.875</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2320,20 +2381,24 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1">
+        <v>7.5</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.875</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2344,20 +2409,24 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1">
+        <v>7</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.75</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2368,20 +2437,26 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1">
+        <v>5</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.25</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2392,20 +2467,24 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1">
+        <v>6.5</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.625</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2416,7 +2495,7 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="13"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -2428,8 +2507,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2440,20 +2521,24 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1">
+        <v>7</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.75</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2464,20 +2549,24 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1">
+        <v>6.5</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.625</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2488,20 +2577,24 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1">
+        <v>7</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.75</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2512,20 +2605,24 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1">
+        <v>7</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.75</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2536,20 +2633,26 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1">
+        <v>5.5</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.375</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2560,20 +2663,26 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1">
+        <v>5</v>
+      </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.25</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2584,20 +2693,24 @@
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1">
+        <v>6</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.5</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2608,7 +2721,7 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="1"/>
+      <c r="D18" s="13"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -2620,8 +2733,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2632,7 +2749,7 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="1"/>
+      <c r="D19" s="13"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -2644,8 +2761,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2656,20 +2777,24 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="1"/>
+      <c r="D20" s="1">
+        <v>6.5</v>
+      </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.625</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2680,20 +2805,26 @@
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="1"/>
+      <c r="D21" s="1">
+        <v>5.5</v>
+      </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.375</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2704,20 +2835,26 @@
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="1"/>
+      <c r="D22" s="1">
+        <v>5.5</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.375</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2728,20 +2865,24 @@
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="1"/>
+      <c r="D23" s="1">
+        <v>7.5</v>
+      </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.875</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2752,20 +2893,24 @@
       <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="1"/>
+      <c r="D24" s="1">
+        <v>6.5</v>
+      </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.625</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2776,20 +2921,26 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="1"/>
+      <c r="D25" s="1">
+        <v>5</v>
+      </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.25</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2800,7 +2951,7 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="1"/>
+      <c r="D26" s="13"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -2812,8 +2963,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2824,7 +2977,7 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="1"/>
+      <c r="D27" s="13"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -2836,8 +2989,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2848,20 +3003,24 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="1"/>
+      <c r="D28" s="1">
+        <v>6.5</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.625</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2872,7 +3031,7 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="1"/>
+      <c r="D29" s="14"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -2884,8 +3043,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2896,20 +3059,24 @@
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="1"/>
+      <c r="D30" s="1">
+        <v>7.5</v>
+      </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1.875</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2920,7 +3087,7 @@
       <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="14"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -2932,12 +3099,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="J31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K31" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H1:I2"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/TME 2-1/Regular Assessment TME 2-1.xlsx
+++ b/TME 2-1/Regular Assessment TME 2-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C38B05B-FC23-4903-97BF-F6A9D03FF6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA6B776-8158-4E94-9BA7-158206804DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TME 2-1 Attendance" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="53">
   <si>
     <t>SL</t>
   </si>
@@ -686,7 +686,8 @@
     <col min="7" max="8" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="24" width="25.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="24" width="25.77734375" style="2" customWidth="1"/>
     <col min="25" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -839,7 +840,9 @@
       <c r="J3" s="4">
         <v>46271</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="K3" s="4">
+        <v>46274</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -962,7 +965,7 @@
       </c>
       <c r="D6" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>32</v>
@@ -982,7 +985,9 @@
       <c r="J6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="D9" s="11">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>32</v>
@@ -1126,7 +1131,9 @@
       <c r="J9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -1202,7 +1209,7 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>32</v>
@@ -1222,7 +1229,9 @@
       <c r="J11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1250,7 +1259,7 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>32</v>
@@ -1270,7 +1279,9 @@
       <c r="J12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -1298,7 +1309,7 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>32</v>
@@ -1318,7 +1329,9 @@
       <c r="J13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -1346,7 +1359,7 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>32</v>
@@ -1366,7 +1379,9 @@
       <c r="J14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -1394,7 +1409,7 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>31</v>
@@ -1414,7 +1429,9 @@
       <c r="J15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1490,7 +1507,7 @@
       </c>
       <c r="D17" s="11">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>32</v>
@@ -1510,7 +1527,9 @@
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -1538,7 +1557,7 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>32</v>
@@ -1558,7 +1577,9 @@
       <c r="J18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="K18" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -1586,7 +1607,7 @@
       </c>
       <c r="D19" s="11">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>31</v>
@@ -1606,7 +1627,9 @@
       <c r="J19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -1730,7 +1753,7 @@
       </c>
       <c r="D22" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>32</v>
@@ -1750,7 +1773,9 @@
       <c r="J22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -1778,7 +1803,7 @@
       </c>
       <c r="D23" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>32</v>
@@ -1798,7 +1823,9 @@
       <c r="J23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2114,7 +2141,7 @@
       </c>
       <c r="D30" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>32</v>
@@ -2134,7 +2161,9 @@
       <c r="J30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -2162,7 +2191,7 @@
       </c>
       <c r="D31" s="11">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>31</v>
@@ -2182,7 +2211,9 @@
       <c r="J31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K31" s="1"/>
+      <c r="K31" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>

--- a/TME 2-1/Regular Assessment TME 2-1.xlsx
+++ b/TME 2-1/Regular Assessment TME 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA6B776-8158-4E94-9BA7-158206804DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2428C73C-62AD-4F86-B32F-E219386C4BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="53">
   <si>
     <t>SL</t>
   </si>
@@ -377,7 +377,7 @@
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -395,6 +395,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -869,7 +879,7 @@
       </c>
       <c r="D4" s="11">
         <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>32</v>
@@ -889,7 +899,9 @@
       <c r="J4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -937,7 +949,9 @@
       <c r="J5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -985,7 +999,7 @@
       <c r="J6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L6" s="1"/>
@@ -1035,7 +1049,9 @@
       <c r="J7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -1083,7 +1099,9 @@
       <c r="J8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1131,7 +1149,7 @@
       <c r="J9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L9" s="1"/>
@@ -1161,7 +1179,7 @@
       </c>
       <c r="D10" s="11">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>31</v>
@@ -1181,7 +1199,9 @@
       <c r="J10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -1229,7 +1249,7 @@
       <c r="J11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L11" s="1"/>
@@ -1279,7 +1299,7 @@
       <c r="J12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L12" s="1"/>
@@ -1329,7 +1349,7 @@
       <c r="J13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L13" s="1"/>
@@ -1379,7 +1399,7 @@
       <c r="J14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L14" s="1"/>
@@ -1429,7 +1449,7 @@
       <c r="J15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L15" s="1"/>
@@ -1479,7 +1499,9 @@
       <c r="J16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -1527,7 +1549,7 @@
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L17" s="1"/>
@@ -1577,7 +1599,7 @@
       <c r="J18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L18" s="1"/>
@@ -1627,7 +1649,7 @@
       <c r="J19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L19" s="1"/>
@@ -1677,7 +1699,9 @@
       <c r="J20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -1725,7 +1749,9 @@
       <c r="J21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -1773,7 +1799,7 @@
       <c r="J22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L22" s="1"/>
@@ -1823,7 +1849,7 @@
       <c r="J23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L23" s="1"/>
@@ -1853,7 +1879,7 @@
       </c>
       <c r="D24" s="11">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>32</v>
@@ -1873,7 +1899,9 @@
       <c r="J24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -1921,7 +1949,9 @@
       <c r="J25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -1949,7 +1979,7 @@
       </c>
       <c r="D26" s="11">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>31</v>
@@ -1969,7 +1999,9 @@
       <c r="J26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="D27" s="11">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>32</v>
@@ -2017,7 +2049,9 @@
       <c r="J27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -2045,7 +2079,7 @@
       </c>
       <c r="D28" s="11">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>31</v>
@@ -2065,7 +2099,9 @@
       <c r="J28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -2093,7 +2129,7 @@
       </c>
       <c r="D29" s="11">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>31</v>
@@ -2113,7 +2149,9 @@
       <c r="J29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -2161,7 +2199,7 @@
       <c r="J30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L30" s="1"/>
@@ -2211,7 +2249,7 @@
       <c r="J31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" s="5" t="s">
         <v>31</v>
       </c>
       <c r="L31" s="1"/>
@@ -2234,11 +2272,19 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
+      <formula>0.6</formula>
+      <formula>0.89</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D31">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="lessThan">
-      <formula>0.8</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D31">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TME 2-1/Regular Assessment TME 2-1.xlsx
+++ b/TME 2-1/Regular Assessment TME 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2428C73C-62AD-4F86-B32F-E219386C4BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6234492-C1DC-4842-A15D-DCFBC6901771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$G$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TME 2-1 Attendance'!$A$3:$X$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TME 2-1 Attendance'!$A$3:$Y$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="54">
   <si>
     <t>SL</t>
   </si>
@@ -198,6 +220,9 @@
   </si>
   <si>
     <t>Comments on Assignment 2</t>
+  </si>
+  <si>
+    <t>Marks</t>
   </si>
 </sst>
 </file>
@@ -242,7 +267,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,12 +309,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -319,7 +338,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -360,9 +379,6 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -377,7 +393,27 @@
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -405,6 +441,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -684,33 +730,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="24" width="25.77734375" style="2" customWidth="1"/>
-    <col min="25" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="25" width="20.77734375" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="14"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D1" s="7"/>
-      <c r="E1" s="8"/>
+      <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
@@ -730,8 +778,9 @@
       <c r="V1" s="8"/>
       <c r="W1" s="8"/>
       <c r="X1" s="8"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y1" s="8"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -743,83 +792,84 @@
         <v>36</v>
       </c>
       <c r="D2" s="7"/>
-      <c r="E2" s="9">
+      <c r="E2" s="7"/>
+      <c r="F2" s="9">
         <v>1</v>
       </c>
-      <c r="F2" s="9">
+      <c r="G2" s="9">
         <v>2</v>
       </c>
-      <c r="G2" s="9">
+      <c r="H2" s="9">
         <v>3</v>
       </c>
-      <c r="H2" s="9">
+      <c r="I2" s="9">
         <v>4</v>
       </c>
-      <c r="I2" s="9">
+      <c r="J2" s="9">
         <v>5</v>
       </c>
-      <c r="J2" s="9">
-        <f>I2+1</f>
+      <c r="K2" s="9">
+        <f>J2+1</f>
         <v>6</v>
       </c>
-      <c r="K2" s="9">
-        <f t="shared" ref="K2:X2" si="0">J2+1</f>
+      <c r="L2" s="9">
+        <f t="shared" ref="L2:Y2" si="0">K2+1</f>
         <v>7</v>
       </c>
-      <c r="L2" s="9">
+      <c r="M2" s="9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M2" s="9">
+      <c r="N2" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="N2" s="9">
+      <c r="O2" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O2" s="9">
+      <c r="P2" s="9">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="P2" s="9">
+      <c r="Q2" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="R2" s="9">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="R2" s="9">
+      <c r="S2" s="9">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="S2" s="9">
+      <c r="T2" s="9">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="T2" s="9">
+      <c r="U2" s="9">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U2" s="9">
-        <f>T2+1</f>
+      <c r="V2" s="9">
+        <f>U2+1</f>
         <v>17</v>
       </c>
-      <c r="V2" s="9">
+      <c r="W2" s="9">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="W2" s="9">
+      <c r="X2" s="9">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="X2" s="9">
+      <c r="Y2" s="9">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -832,29 +882,33 @@
       <c r="D3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4">
         <v>46250</v>
       </c>
-      <c r="F3" s="4">
+      <c r="G3" s="4">
         <v>46254</v>
       </c>
-      <c r="G3" s="4">
+      <c r="H3" s="4">
         <v>46257</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="4">
         <v>46264</v>
       </c>
-      <c r="I3" s="4">
+      <c r="J3" s="4">
         <v>46267</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <v>46271</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>46274</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="M3" s="4">
+        <v>46278</v>
+      </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
@@ -866,8 +920,9 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y3" s="4"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -878,11 +933,12 @@
         <v>3</v>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
+        <f t="shared" ref="D4:D31" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
         <v>0.8571428571428571</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>32</v>
+      <c r="E4" s="1" cm="1">
+        <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>32</v>
@@ -890,11 +946,11 @@
       <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
+      <c r="H4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>32</v>
@@ -902,7 +958,9 @@
       <c r="K4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="1"/>
+      <c r="L4" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -915,10 +973,11 @@
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y4" s="1"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
-        <f t="shared" ref="A5:A31" si="1">A4+1</f>
+        <f t="shared" ref="A5:A31" si="2">A4+1</f>
         <v>2</v>
       </c>
       <c r="B5" s="1">
@@ -928,11 +987,12 @@
         <v>4</v>
       </c>
       <c r="D5" s="11">
-        <f t="shared" ref="D5:D31" si="2">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>32</v>
+      <c r="E5" s="1" cm="1">
+        <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>32</v>
@@ -952,7 +1012,9 @@
       <c r="K5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -965,10 +1027,11 @@
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y5" s="1"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -978,11 +1041,12 @@
         <v>5</v>
       </c>
       <c r="D6" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>32</v>
+      <c r="E6" s="1" cm="1">
+        <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>32</v>
@@ -999,10 +1063,12 @@
       <c r="J6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -1015,10 +1081,11 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y6" s="1"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="B7" s="1">
@@ -1028,11 +1095,12 @@
         <v>6</v>
       </c>
       <c r="D7" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>32</v>
+      <c r="E7" s="1" cm="1">
+        <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>32</v>
@@ -1052,7 +1120,9 @@
       <c r="K7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -1065,10 +1135,11 @@
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y7" s="1"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -1078,11 +1149,12 @@
         <v>7</v>
       </c>
       <c r="D8" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>32</v>
+      <c r="E8" s="1" cm="1">
+        <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>32</v>
@@ -1102,7 +1174,9 @@
       <c r="K8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -1115,10 +1189,11 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y8" s="1"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="B9" s="1">
@@ -1128,31 +1203,34 @@
         <v>8</v>
       </c>
       <c r="D9" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>32</v>
+      <c r="E9" s="1" cm="1">
+        <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1165,10 +1243,11 @@
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y9" s="1"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -1178,32 +1257,37 @@
         <v>9</v>
       </c>
       <c r="D10" s="11">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="1" cm="1">
+        <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1215,10 +1299,11 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y10" s="1"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B11" s="1">
@@ -1228,11 +1313,12 @@
         <v>10</v>
       </c>
       <c r="D11" s="11">
-        <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.625</v>
+      </c>
+      <c r="E11" s="1" cm="1">
+        <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>32</v>
@@ -1243,17 +1329,21 @@
       <c r="H11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -1265,10 +1355,11 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y11" s="1"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B12" s="1">
@@ -1278,11 +1369,12 @@
         <v>11</v>
       </c>
       <c r="D12" s="11">
-        <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.625</v>
+      </c>
+      <c r="E12" s="1" cm="1">
+        <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>32</v>
@@ -1296,14 +1388,18 @@
       <c r="I12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="5" t="s">
-        <v>31</v>
+      <c r="J12" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="L12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -1315,10 +1411,11 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y12" s="1"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
@@ -1328,11 +1425,12 @@
         <v>12</v>
       </c>
       <c r="D13" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>32</v>
+      <c r="E13" s="1" cm="1">
+        <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>32</v>
@@ -1349,10 +1447,12 @@
       <c r="J13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1365,10 +1465,11 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y13" s="1"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B14" s="1">
@@ -1378,11 +1479,12 @@
         <v>13</v>
       </c>
       <c r="D14" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>32</v>
+      <c r="E14" s="1" cm="1">
+        <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>32</v>
@@ -1393,16 +1495,18 @@
       <c r="H14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1415,10 +1519,11 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y14" s="1"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="B15" s="1">
@@ -1428,32 +1533,37 @@
         <v>14</v>
       </c>
       <c r="D15" s="11">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="E15" s="1" cm="1">
+        <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>31</v>
+      <c r="J15" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="L15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
@@ -1465,10 +1575,11 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y15" s="1"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="B16" s="1">
@@ -1478,11 +1589,12 @@
         <v>15</v>
       </c>
       <c r="D16" s="11">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E16" s="1" cm="1">
+        <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>32</v>
@@ -1502,8 +1614,12 @@
       <c r="K16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
@@ -1515,10 +1631,11 @@
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y16" s="1"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="B17" s="1">
@@ -1528,20 +1645,21 @@
         <v>16</v>
       </c>
       <c r="D17" s="11">
-        <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.625</v>
+      </c>
+      <c r="E17" s="1" cm="1">
+        <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
+        <v>3</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>32</v>
+      <c r="G17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>32</v>
@@ -1549,11 +1667,15 @@
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -1565,10 +1687,11 @@
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y17" s="1"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="B18" s="1">
@@ -1578,14 +1701,15 @@
         <v>17</v>
       </c>
       <c r="D18" s="11">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>31</v>
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="E18" s="1" cm="1">
+        <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>31</v>
@@ -1593,17 +1717,21 @@
       <c r="H18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>31</v>
+      <c r="I18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
+      <c r="L18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -1615,10 +1743,11 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y18" s="1"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="B19" s="1">
@@ -1628,17 +1757,18 @@
         <v>18</v>
       </c>
       <c r="D19" s="11">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>31</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="1" cm="1">
+        <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
+        <v>0</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>32</v>
+      <c r="G19" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>32</v>
@@ -1649,11 +1779,15 @@
       <c r="J19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1665,10 +1799,11 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y19" s="1"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -1678,11 +1813,12 @@
         <v>19</v>
       </c>
       <c r="D20" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>32</v>
+      <c r="E20" s="1" cm="1">
+        <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>32</v>
@@ -1702,7 +1838,9 @@
       <c r="K20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -1715,10 +1853,11 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y20" s="1"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="B21" s="1">
@@ -1728,11 +1867,12 @@
         <v>20</v>
       </c>
       <c r="D21" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>32</v>
+      <c r="E21" s="1" cm="1">
+        <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>32</v>
@@ -1752,7 +1892,9 @@
       <c r="K21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -1765,10 +1907,11 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y21" s="1"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="B22" s="1">
@@ -1778,11 +1921,12 @@
         <v>21</v>
       </c>
       <c r="D22" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>32</v>
+      <c r="E22" s="1" cm="1">
+        <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>32</v>
@@ -1799,10 +1943,12 @@
       <c r="J22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K22" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -1815,10 +1961,11 @@
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y22" s="1"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="B23" s="1">
@@ -1828,11 +1975,12 @@
         <v>22</v>
       </c>
       <c r="D23" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>32</v>
+      <c r="E23" s="1" cm="1">
+        <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>32</v>
@@ -1849,10 +1997,12 @@
       <c r="J23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -1865,10 +2015,11 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y23" s="1"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="B24" s="1">
@@ -1878,11 +2029,12 @@
         <v>23</v>
       </c>
       <c r="D24" s="11">
-        <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E24" s="1" cm="1">
+        <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>32</v>
@@ -1893,17 +2045,21 @@
       <c r="H24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>32</v>
+      <c r="I24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -1915,10 +2071,11 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y24" s="1"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="B25" s="1">
@@ -1928,11 +2085,12 @@
         <v>24</v>
       </c>
       <c r="D25" s="11">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+      <c r="E25" s="1" cm="1">
+        <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>32</v>
@@ -1952,8 +2110,12 @@
       <c r="K25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -1965,10 +2127,11 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y25" s="1"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="B26" s="1">
@@ -1978,20 +2141,21 @@
         <v>25</v>
       </c>
       <c r="D26" s="11">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="E26" s="1" cm="1">
+        <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>31</v>
+      <c r="H26" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>31</v>
@@ -1999,11 +2163,15 @@
       <c r="J26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
+      <c r="K26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -2015,10 +2183,11 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y26" s="1"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="B27" s="1">
@@ -2028,17 +2197,18 @@
         <v>26</v>
       </c>
       <c r="D27" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>32</v>
+      <c r="E27" s="1" cm="1">
+        <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
+        <v>6</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>32</v>
@@ -2052,7 +2222,9 @@
       <c r="K27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -2065,10 +2237,11 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y27" s="1"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="B28" s="1">
@@ -2078,14 +2251,15 @@
         <v>27</v>
       </c>
       <c r="D28" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>32</v>
+      <c r="E28" s="1" cm="1">
+        <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
+        <v>6</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>32</v>
@@ -2102,7 +2276,9 @@
       <c r="K28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L28" s="1"/>
+      <c r="L28" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
@@ -2115,10 +2291,11 @@
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y28" s="1"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="B29" s="1">
@@ -2128,14 +2305,15 @@
         <v>28</v>
       </c>
       <c r="D29" s="11">
-        <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="E29" s="1" cm="1">
+        <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>32</v>
@@ -2152,8 +2330,12 @@
       <c r="K29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
+      <c r="L29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
@@ -2165,10 +2347,11 @@
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y29" s="1"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="B30" s="1">
@@ -2178,11 +2361,12 @@
         <v>29</v>
       </c>
       <c r="D30" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>32</v>
+      <c r="E30" s="1" cm="1">
+        <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
+        <v>6</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>32</v>
@@ -2199,10 +2383,12 @@
       <c r="J30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -2215,10 +2401,11 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y30" s="1"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="B31" s="1">
@@ -2228,32 +2415,37 @@
         <v>30</v>
       </c>
       <c r="D31" s="11">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="1" cm="1">
+        <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>32</v>
+      <c r="H31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
+      <c r="K31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
@@ -2265,26 +2457,35 @@
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:X31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:Y31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>0.6</formula>
-      <formula>0.89</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
+      <formula>0.6</formula>
+      <formula>0.79</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
+      <formula>0.79</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0.9</formula>
+  <conditionalFormatting sqref="E4:E31">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+      <formula>3</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D31">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>0.6</formula>
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="between">
+      <formula>2</formula>
+      <formula>5.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
+      <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2309,10 +2510,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="14"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
@@ -2328,14 +2529,14 @@
       <c r="G1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17" t="s">
+      <c r="I1" s="15"/>
+      <c r="J1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="16" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2356,10 +2557,10 @@
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
     </row>
     <row r="3" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -2389,8 +2590,8 @@
       <c r="I3" s="12">
         <v>7.5</v>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
@@ -3108,17 +3309,19 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="14"/>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>44</v>
@@ -3164,17 +3367,19 @@
       <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="14"/>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>44</v>

--- a/TME 2-1/Regular Assessment TME 2-1.xlsx
+++ b/TME 2-1/Regular Assessment TME 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6234492-C1DC-4842-A15D-DCFBC6901771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45A754C-5B77-4EFF-8B4B-AFE742E3B541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="55">
   <si>
     <t>SL</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>Marks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drew 2 Figures  </t>
   </si>
 </sst>
 </file>
@@ -338,7 +341,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -386,6 +389,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -745,7 +751,8 @@
     <col min="11" max="11" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="36.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="25" width="20.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="41" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="25" width="29.88671875" style="2" customWidth="1"/>
     <col min="26" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -909,7 +916,9 @@
       <c r="M3" s="4">
         <v>46278</v>
       </c>
-      <c r="N3" s="4"/>
+      <c r="N3" s="4">
+        <v>46281</v>
+      </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -934,7 +943,7 @@
       </c>
       <c r="D4" s="11">
         <f t="shared" ref="D4:D31" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.8571428571428571</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
@@ -961,8 +970,12 @@
       <c r="L4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1015,8 +1028,12 @@
       <c r="L5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -1042,7 +1059,7 @@
       </c>
       <c r="D6" s="11">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
@@ -1069,8 +1086,12 @@
       <c r="L6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1123,8 +1144,12 @@
       <c r="L7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -1177,8 +1202,12 @@
       <c r="L8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1204,11 +1233,11 @@
       </c>
       <c r="D9" s="11">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>32</v>
@@ -1231,8 +1260,12 @@
       <c r="L9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1258,7 +1291,7 @@
       </c>
       <c r="D10" s="11">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1288,7 +1321,9 @@
       <c r="M10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1314,7 +1349,7 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E11" s="1" cm="1">
         <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
@@ -1344,7 +1379,9 @@
       <c r="M11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1370,11 +1407,11 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="E12" s="1" cm="1">
         <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>32</v>
@@ -1400,7 +1437,9 @@
       <c r="M12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N12" s="1"/>
+      <c r="N12" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -1426,11 +1465,11 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E13" s="1" cm="1">
         <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>32</v>
@@ -1453,8 +1492,12 @@
       <c r="L13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
@@ -1480,7 +1523,7 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
@@ -1507,8 +1550,12 @@
       <c r="L14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -1534,7 +1581,7 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E15" s="1" cm="1">
         <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
@@ -1564,7 +1611,9 @@
       <c r="M15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N15" s="1"/>
+      <c r="N15" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
@@ -1590,7 +1639,7 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E16" s="1" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
@@ -1620,7 +1669,9 @@
       <c r="M16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N16" s="1"/>
+      <c r="N16" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
@@ -1646,7 +1697,7 @@
       </c>
       <c r="D17" s="11">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
@@ -1676,7 +1727,9 @@
       <c r="M17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N17" s="1"/>
+      <c r="N17" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
@@ -1702,7 +1755,7 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
@@ -1732,7 +1785,9 @@
       <c r="M18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N18" s="1"/>
+      <c r="N18" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -1758,7 +1813,7 @@
       </c>
       <c r="D19" s="11">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1788,7 +1843,9 @@
       <c r="M19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N19" s="1"/>
+      <c r="N19" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
@@ -1841,8 +1898,12 @@
       <c r="L20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
+      <c r="M20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
@@ -1868,11 +1929,11 @@
       </c>
       <c r="D21" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E21" s="1" cm="1">
         <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>32</v>
@@ -1895,8 +1956,12 @@
       <c r="L21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
+      <c r="M21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -1922,7 +1987,7 @@
       </c>
       <c r="D22" s="11">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E22" s="1" cm="1">
         <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
@@ -1949,8 +2014,12 @@
       <c r="L22" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -1976,7 +2045,7 @@
       </c>
       <c r="D23" s="11">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
@@ -2003,8 +2072,12 @@
       <c r="L23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -2030,11 +2103,11 @@
       </c>
       <c r="D24" s="11">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>32</v>
@@ -2060,7 +2133,9 @@
       <c r="M24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N24" s="1"/>
+      <c r="N24" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -2086,11 +2161,11 @@
       </c>
       <c r="D25" s="11">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>32</v>
@@ -2116,7 +2191,9 @@
       <c r="M25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N25" s="1"/>
+      <c r="N25" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -2142,7 +2219,7 @@
       </c>
       <c r="D26" s="11">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="E26" s="1" cm="1">
         <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
@@ -2172,7 +2249,9 @@
       <c r="M26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N26" s="1"/>
+      <c r="N26" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -2198,7 +2277,7 @@
       </c>
       <c r="D27" s="11">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
@@ -2225,8 +2304,12 @@
       <c r="L27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -2252,7 +2335,7 @@
       </c>
       <c r="D28" s="11">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
@@ -2279,8 +2362,12 @@
       <c r="L28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
@@ -2306,7 +2393,7 @@
       </c>
       <c r="D29" s="11">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
@@ -2336,7 +2423,9 @@
       <c r="M29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
@@ -2362,7 +2451,7 @@
       </c>
       <c r="D30" s="11">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
@@ -2389,8 +2478,12 @@
       <c r="L30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
@@ -2416,7 +2509,7 @@
       </c>
       <c r="D31" s="11">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
@@ -2446,7 +2539,9 @@
       <c r="M31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N31" s="1"/>
+      <c r="N31" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
@@ -2999,17 +3094,19 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="13"/>
+      <c r="D18" s="17">
+        <v>5.5</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>45</v>
@@ -3027,17 +3124,19 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="13"/>
+      <c r="D19" s="17">
+        <v>4</v>
+      </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>47</v>
@@ -3255,19 +3354,23 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="13"/>
+      <c r="D27" s="17">
+        <v>4</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="K27" s="1"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">

--- a/TME 2-1/Regular Assessment TME 2-1.xlsx
+++ b/TME 2-1/Regular Assessment TME 2-1.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45A754C-5B77-4EFF-8B4B-AFE742E3B541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27A1D6A-4B11-4B58-B7BA-4A38E600C04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TME 2-1 Attendance" sheetId="2" r:id="rId1"/>
-    <sheet name="Assessment" sheetId="3" r:id="rId2"/>
+    <sheet name="Assignment" sheetId="3" r:id="rId2"/>
+    <sheet name="Class Test" sheetId="4" r:id="rId3"/>
+    <sheet name="Eval." sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!$A$3:$G$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TME 2-1 Attendance'!$A$3:$Y$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assignment!$A$3:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Class Test'!$A$3:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Eval.!$A$3:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TME 2-1 Attendance'!$A$3:$T$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="60">
   <si>
     <t>SL</t>
   </si>
@@ -183,42 +187,18 @@
     <t>Knitting Action</t>
   </si>
   <si>
-    <t>Assignmnet 2</t>
-  </si>
-  <si>
-    <t>Assignment 3</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
     <t>7.5</t>
   </si>
   <si>
-    <t>Not Clear</t>
-  </si>
-  <si>
     <t>Drew 3 Figures</t>
   </si>
   <si>
-    <t xml:space="preserve">Underlapping, Yarn Feeding, Pressing Mistakes </t>
-  </si>
-  <si>
-    <t>Drew 2 Figures &amp; SJCKM</t>
-  </si>
-  <si>
-    <t>Drew 3 Figures &amp; SJCKM</t>
-  </si>
-  <si>
-    <t>Drew 3 Figures, Knock Over Missing, Pressing Mistake</t>
-  </si>
-  <si>
     <t>Comments on Assignment 1</t>
   </si>
   <si>
-    <t>Assignment 4</t>
-  </si>
-  <si>
     <t>Comments on Assignment 2</t>
   </si>
   <si>
@@ -226,6 +206,45 @@
   </si>
   <si>
     <t xml:space="preserve">Drew 2 Figures  </t>
+  </si>
+  <si>
+    <t>Omit some actions</t>
+  </si>
+  <si>
+    <t>Drew 3 Figures &amp; Omit some actions</t>
+  </si>
+  <si>
+    <t>Drew 2 Figures</t>
+  </si>
+  <si>
+    <t>Drew 3 Figures, Omit some actions</t>
+  </si>
+  <si>
+    <t>Drawing Not Clear</t>
+  </si>
+  <si>
+    <t>NOAS</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>Tuck, Miss</t>
+  </si>
+  <si>
+    <t>BOEV</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>Assignment</t>
+  </si>
+  <si>
+    <t>Class Test</t>
+  </si>
+  <si>
+    <t>Assignment 2</t>
   </si>
 </sst>
 </file>
@@ -235,7 +254,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,8 +288,29 @@
       <name val="Gill Sans MT"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,12 +348,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -336,12 +400,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -376,22 +466,34 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -736,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.21875" style="2" bestFit="1" customWidth="1"/>
@@ -752,15 +854,16 @@
     <col min="12" max="12" width="39.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="36.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="41" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="25" width="29.88671875" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="2"/>
+    <col min="15" max="15" width="36.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="29.88671875" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="16"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
@@ -781,13 +884,8 @@
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
       <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -796,7 +894,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
@@ -820,7 +918,7 @@
         <v>6</v>
       </c>
       <c r="L2" s="9">
-        <f t="shared" ref="L2:Y2" si="0">K2+1</f>
+        <f t="shared" ref="L2:T2" si="0">K2+1</f>
         <v>7</v>
       </c>
       <c r="M2" s="9">
@@ -855,28 +953,8 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="U2" s="9">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="V2" s="9">
-        <f>U2+1</f>
-        <v>17</v>
-      </c>
-      <c r="W2" s="9">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="X2" s="9">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="Y2" s="9">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -890,7 +968,7 @@
         <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F3" s="4">
         <v>46250</v>
@@ -919,19 +997,16 @@
       <c r="N3" s="4">
         <v>46281</v>
       </c>
-      <c r="O3" s="4"/>
+      <c r="O3" s="4">
+        <v>46292</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -942,12 +1017,12 @@
         <v>3</v>
       </c>
       <c r="D4" s="11">
-        <f t="shared" ref="D4:D31" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.88888888888888884</v>
+        <f t="shared" ref="D4:D31" si="1">COUNTIF(F4:T4,"P")/(COUNTIF(F4:T4,"P")+COUNTIF(F4:T4,"A"))</f>
+        <v>0.9</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>32</v>
@@ -976,19 +1051,16 @@
       <c r="N4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A31" si="2">A4+1</f>
         <v>2</v>
@@ -1034,19 +1106,16 @@
       <c r="N5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="1"/>
+      <c r="O5" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
@@ -1059,11 +1128,11 @@
       </c>
       <c r="D6" s="11">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>32</v>
@@ -1092,19 +1161,16 @@
       <c r="N6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -1150,19 +1216,16 @@
       <c r="N7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1208,19 +1271,16 @@
       <c r="N8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O8" s="1"/>
+      <c r="O8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1233,11 +1293,11 @@
       </c>
       <c r="D9" s="11">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>32</v>
@@ -1266,19 +1326,16 @@
       <c r="N9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O9" s="1"/>
+      <c r="O9" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -1291,7 +1348,7 @@
       </c>
       <c r="D10" s="11">
         <f t="shared" si="1"/>
-        <v>0.55555555555555558</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1324,19 +1381,16 @@
       <c r="N10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O10" s="1"/>
+      <c r="O10" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -1349,11 +1403,11 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7</v>
       </c>
       <c r="E11" s="1" cm="1">
         <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>32</v>
@@ -1382,19 +1436,16 @@
       <c r="N11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O11" s="1"/>
+      <c r="O11" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -1407,11 +1458,11 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="1"/>
-        <v>0.55555555555555558</v>
+        <v>0.6</v>
       </c>
       <c r="E12" s="1" cm="1">
         <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>32</v>
@@ -1440,19 +1491,16 @@
       <c r="N12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="1"/>
+      <c r="O12" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -1465,11 +1513,11 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E13" s="1" cm="1">
         <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>32</v>
@@ -1498,19 +1546,16 @@
       <c r="N13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="1"/>
+      <c r="O13" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1523,11 +1568,11 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>32</v>
@@ -1556,19 +1601,16 @@
       <c r="N14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O14" s="1"/>
+      <c r="O14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -1581,7 +1623,7 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.4</v>
       </c>
       <c r="E15" s="1" cm="1">
         <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
@@ -1614,19 +1656,16 @@
       <c r="N15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="1"/>
+      <c r="O15" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -1639,11 +1678,11 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E16" s="1" cm="1">
         <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>32</v>
@@ -1672,19 +1711,16 @@
       <c r="N16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O16" s="1"/>
+      <c r="O16" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -1697,11 +1733,11 @@
       </c>
       <c r="D17" s="11">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>32</v>
@@ -1730,19 +1766,16 @@
       <c r="N17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O17" s="1"/>
+      <c r="O17" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1755,7 +1788,7 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="1"/>
-        <v>0.22222222222222221</v>
+        <v>0.2</v>
       </c>
       <c r="E18" s="1" cm="1">
         <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
@@ -1788,19 +1821,16 @@
       <c r="N18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O18" s="1"/>
+      <c r="O18" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -1813,7 +1843,7 @@
       </c>
       <c r="D19" s="11">
         <f t="shared" si="1"/>
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1846,19 +1876,16 @@
       <c r="N19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O19" s="1"/>
+      <c r="O19" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -1904,19 +1931,16 @@
       <c r="N20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O20" s="1"/>
+      <c r="O20" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -1929,11 +1953,11 @@
       </c>
       <c r="D21" s="11">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E21" s="1" cm="1">
         <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>32</v>
@@ -1962,19 +1986,16 @@
       <c r="N21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O21" s="1"/>
+      <c r="O21" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -1987,11 +2008,11 @@
       </c>
       <c r="D22" s="11">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E22" s="1" cm="1">
         <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>32</v>
@@ -2020,19 +2041,16 @@
       <c r="N22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O22" s="1"/>
+      <c r="O22" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -2045,11 +2063,11 @@
       </c>
       <c r="D23" s="11">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>32</v>
@@ -2078,19 +2096,16 @@
       <c r="N23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O23" s="1"/>
+      <c r="O23" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -2103,11 +2118,11 @@
       </c>
       <c r="D24" s="11">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.7</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>32</v>
@@ -2136,19 +2151,16 @@
       <c r="N24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -2161,11 +2173,11 @@
       </c>
       <c r="D25" s="11">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>32</v>
@@ -2194,19 +2206,16 @@
       <c r="N25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O25" s="1"/>
+      <c r="O25" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2219,7 +2228,7 @@
       </c>
       <c r="D26" s="11">
         <f t="shared" si="1"/>
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="E26" s="1" cm="1">
         <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
@@ -2252,19 +2261,16 @@
       <c r="N26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O26" s="1"/>
+      <c r="O26" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2277,11 +2283,11 @@
       </c>
       <c r="D27" s="11">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E27" s="1" cm="1">
         <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>32</v>
@@ -2310,19 +2316,16 @@
       <c r="N27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O27" s="1"/>
+      <c r="O27" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2335,11 +2338,11 @@
       </c>
       <c r="D28" s="11">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>31</v>
@@ -2368,19 +2371,16 @@
       <c r="N28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O28" s="1"/>
+      <c r="O28" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="D29" s="11">
         <f t="shared" si="1"/>
-        <v>0.77777777777777779</v>
+        <v>0.8</v>
       </c>
       <c r="E29" s="1" cm="1">
         <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>31</v>
@@ -2426,19 +2426,16 @@
       <c r="N29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O29" s="1"/>
+      <c r="O29" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2451,11 +2448,11 @@
       </c>
       <c r="D30" s="11">
         <f t="shared" si="1"/>
-        <v>0.88888888888888884</v>
+        <v>0.9</v>
       </c>
       <c r="E30" s="1" cm="1">
         <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>32</v>
@@ -2484,19 +2481,16 @@
       <c r="N30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O30" s="1"/>
+      <c r="O30" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2509,7 +2503,7 @@
       </c>
       <c r="D31" s="11">
         <f t="shared" si="1"/>
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
@@ -2542,20 +2536,17 @@
       <c r="N31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O31" s="1"/>
+      <c r="O31" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Y31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:T31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -2590,52 +2581,46 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A66B3EF-818E-4A70-9374-2DAEC6B795EE}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" style="2" customWidth="1"/>
-    <col min="10" max="11" width="52.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="2"/>
+    <col min="4" max="4" width="23.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" style="2" customWidth="1"/>
+    <col min="8" max="9" width="52.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="16"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G1" s="16"/>
+      <c r="H1" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -2644,20 +2629,20 @@
         <v>28</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-    </row>
-    <row r="3" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2668,27 +2653,21 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="3">
+        <v>41</v>
+      </c>
+      <c r="F3" s="3">
         <v>30</v>
       </c>
-      <c r="I3" s="12">
+      <c r="G3" s="3">
         <v>7.5</v>
       </c>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2702,22 +2681,20 @@
         <v>7.5</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1">
-        <f>SUM(D4:G4)</f>
+      <c r="F4" s="1">
+        <f t="shared" ref="F4:F31" si="0">SUM(D4:E4)</f>
         <v>7.5</v>
       </c>
-      <c r="I4" s="1">
-        <f>(H4/30)*7.5</f>
-        <v>1.875</v>
-      </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
-        <f t="shared" ref="A5:A31" si="0">A4+1</f>
+      <c r="G4" s="1">
+        <f>F4/2</f>
+        <v>3.75</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f t="shared" ref="A5:A31" si="1">A4+1</f>
         <v>2</v>
       </c>
       <c r="B5" s="1">
@@ -2730,22 +2707,20 @@
         <v>7.5</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1">
-        <f t="shared" ref="H5:H31" si="1">SUM(D5:G5)</f>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="I5" s="1">
-        <f t="shared" ref="I5:I31" si="2">(H5/30)*7.5</f>
-        <v>1.875</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G31" si="2">F5/2</f>
+        <v>3.75</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -2758,22 +2733,20 @@
         <v>7.5</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1">
-        <f t="shared" si="1"/>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="I6" s="1">
-        <f t="shared" si="2"/>
-        <v>1.875</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G6" s="1">
+        <f t="shared" si="2"/>
+        <v>3.75</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B7" s="1">
@@ -2786,22 +2759,20 @@
         <v>7</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1">
-        <f t="shared" si="1"/>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I7" s="1">
-        <f t="shared" si="2"/>
-        <v>1.75</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G7" s="1">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -2814,24 +2785,22 @@
         <v>5</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1">
-        <f t="shared" si="1"/>
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I8" s="1">
-        <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G8" s="1">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B9" s="1">
@@ -2844,22 +2813,20 @@
         <v>6.5</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1">
-        <f t="shared" si="1"/>
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="I9" s="1">
-        <f t="shared" si="2"/>
-        <v>1.625</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G9" s="1">
+        <f t="shared" si="2"/>
+        <v>3.25</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -2868,24 +2835,22 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="13"/>
+      <c r="D10" s="12"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B11" s="1">
@@ -2898,22 +2863,20 @@
         <v>7</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1">
-        <f t="shared" si="1"/>
+      <c r="F11" s="1">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I11" s="1">
-        <f t="shared" si="2"/>
-        <v>1.75</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G11" s="1">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B12" s="1">
@@ -2926,22 +2889,20 @@
         <v>6.5</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1">
-        <f t="shared" si="1"/>
+      <c r="F12" s="1">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="I12" s="1">
-        <f t="shared" si="2"/>
-        <v>1.625</v>
-      </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G12" s="1">
+        <f t="shared" si="2"/>
+        <v>3.25</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
@@ -2954,22 +2915,20 @@
         <v>7</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1">
-        <f t="shared" si="1"/>
+      <c r="F13" s="1">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I13" s="1">
-        <f t="shared" si="2"/>
-        <v>1.75</v>
-      </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G13" s="1">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B14" s="1">
@@ -2982,22 +2941,20 @@
         <v>7</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1">
-        <f t="shared" si="1"/>
+      <c r="F14" s="1">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I14" s="1">
-        <f t="shared" si="2"/>
-        <v>1.75</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G14" s="1">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="B15" s="1">
@@ -3010,24 +2967,22 @@
         <v>5.5</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1">
-        <f t="shared" si="1"/>
+      <c r="F15" s="1">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="I15" s="1">
-        <f t="shared" si="2"/>
-        <v>1.375</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G15" s="1">
+        <f t="shared" si="2"/>
+        <v>2.75</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B16" s="1">
@@ -3040,24 +2995,21 @@
         <v>5</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="I16" s="1">
-        <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F16" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="2"/>
+        <v>2.75</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B17" s="1">
@@ -3070,22 +3022,20 @@
         <v>6</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1">
-        <f t="shared" si="1"/>
+      <c r="F17" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I17" s="1">
-        <f t="shared" si="2"/>
-        <v>1.5</v>
-      </c>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G17" s="1">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B18" s="1">
@@ -3094,28 +3044,26 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="1">
         <v>5.5</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1">
-        <f t="shared" si="1"/>
+      <c r="F18" s="1">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="I18" s="1">
-        <f t="shared" si="2"/>
-        <v>1.375</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G18" s="1">
+        <f t="shared" si="2"/>
+        <v>2.75</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B19" s="1">
@@ -3124,28 +3072,26 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="17">
-        <v>4</v>
+      <c r="D19" s="1">
+        <v>3.75</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I19" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F19" s="1">
+        <f t="shared" si="0"/>
+        <v>3.75</v>
+      </c>
+      <c r="G19" s="1">
+        <f t="shared" si="2"/>
+        <v>1.875</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -3158,22 +3104,20 @@
         <v>6.5</v>
       </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1">
-        <f t="shared" si="1"/>
+      <c r="F20" s="1">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="I20" s="1">
-        <f t="shared" si="2"/>
-        <v>1.625</v>
-      </c>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G20" s="1">
+        <f t="shared" si="2"/>
+        <v>3.25</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B21" s="1">
@@ -3186,24 +3130,22 @@
         <v>5.5</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1">
-        <f t="shared" si="1"/>
+      <c r="F21" s="1">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="I21" s="1">
-        <f t="shared" si="2"/>
-        <v>1.375</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G21" s="1">
+        <f t="shared" si="2"/>
+        <v>2.75</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B22" s="1">
@@ -3216,24 +3158,22 @@
         <v>5.5</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1">
-        <f t="shared" si="1"/>
+      <c r="F22" s="1">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="I22" s="1">
-        <f t="shared" si="2"/>
-        <v>1.375</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G22" s="1">
+        <f t="shared" si="2"/>
+        <v>2.75</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="B23" s="1">
@@ -3246,22 +3186,20 @@
         <v>7.5</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1">
-        <f t="shared" si="1"/>
+      <c r="F23" s="1">
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="I23" s="1">
-        <f t="shared" si="2"/>
-        <v>1.875</v>
-      </c>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
-        <f t="shared" si="0"/>
+      <c r="G23" s="1">
+        <f t="shared" si="2"/>
+        <v>3.75</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="B24" s="1">
@@ -3274,22 +3212,20 @@
         <v>6.5</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1">
-        <f t="shared" si="1"/>
+      <c r="F24" s="1">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="I24" s="1">
-        <f t="shared" si="2"/>
-        <v>1.625</v>
-      </c>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G24" s="1">
+        <f t="shared" si="2"/>
+        <v>3.25</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="B25" s="1">
@@ -3302,24 +3238,22 @@
         <v>5</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1">
-        <f t="shared" si="1"/>
+      <c r="F25" s="1">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I25" s="1">
-        <f t="shared" si="2"/>
-        <v>1.25</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G25" s="1">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B26" s="1">
@@ -3328,24 +3262,22 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="13"/>
+      <c r="D26" s="12"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F26" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="B27" s="1">
@@ -3354,28 +3286,26 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="17">
-        <v>4</v>
+      <c r="D27" s="1">
+        <v>3.75</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I27" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F27" s="1">
+        <f t="shared" si="0"/>
+        <v>3.75</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="2"/>
+        <v>1.875</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B28" s="1">
@@ -3388,22 +3318,20 @@
         <v>6.5</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1">
-        <f t="shared" si="1"/>
+      <c r="F28" s="1">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="I28" s="1">
-        <f t="shared" si="2"/>
-        <v>1.625</v>
-      </c>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G28" s="1">
+        <f t="shared" si="2"/>
+        <v>3.25</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="B29" s="1">
@@ -3413,27 +3341,25 @@
         <v>28</v>
       </c>
       <c r="D29" s="1">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="I29" s="1">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F29" s="1">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="G29" s="1">
+        <f t="shared" si="2"/>
+        <v>2.25</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="B30" s="1">
@@ -3446,22 +3372,20 @@
         <v>7.5</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1">
-        <f t="shared" si="1"/>
+      <c r="F30" s="1">
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="I30" s="1">
-        <f t="shared" si="2"/>
-        <v>1.875</v>
-      </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G30" s="1">
+        <f t="shared" si="2"/>
+        <v>3.75</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="B31" s="1">
@@ -3471,36 +3395,1330 @@
         <v>30</v>
       </c>
       <c r="D31" s="1">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="I31" s="1">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K31" s="1"/>
+      <c r="F31" s="1">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="G31" s="1">
+        <f t="shared" si="2"/>
+        <v>2.25</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:E31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="H1:I2"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="K1:K3"/>
+    <mergeCell ref="F1:G2"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="I1:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="D3:G3" numberStoredAsText="1"/>
+    <ignoredError sqref="D3:E3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE7D3D1E-0887-48D8-B9E6-CD76EB008C88}">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="7">
+        <f>COUNT(A4:A31)</f>
+        <v>28</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>25011101001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f t="shared" ref="A5:A31" si="0">A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>25011101002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>25011101003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>25011101004</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>25011101005</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>25011101008</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>25011101009</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>25011101010</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>25011101011</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>25011101012</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>25011101013</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>25011101014</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>25011101015</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>25011101016</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>25011101017</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>25011101018</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>25011101019</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>25011101020</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>25011101021</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>25011101022</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>25011101023</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>25011101024</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25011101025</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>25011101026</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>25011101027</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>25011101028</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>25011101029</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>25011101030</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="1"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C159D0FE-8346-4F75-A74F-7071A40E2D26}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="20">
+        <v>7.5</v>
+      </c>
+      <c r="E1" s="20">
+        <v>7.5</v>
+      </c>
+      <c r="F1" s="20">
+        <v>15</v>
+      </c>
+      <c r="G1" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="7">
+        <f>COUNT(A4:A31)</f>
+        <v>28</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>25011101001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1">
+        <f>_xlfn.XLOOKUP(B4,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E4" s="1">
+        <f>_xlfn.XLOOKUP(B4,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.75</v>
+      </c>
+      <c r="F4" s="1">
+        <f>_xlfn.XLOOKUP(B4,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="15">
+        <f>CEILING(SUM(D4:F4),0.5)</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <f t="shared" ref="A5:A31" si="0">A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>25011101002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1">
+        <f>_xlfn.XLOOKUP(B5,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E5" s="1">
+        <f>_xlfn.XLOOKUP(B5,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.75</v>
+      </c>
+      <c r="F5" s="1">
+        <f>_xlfn.XLOOKUP(B5,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="15">
+        <f t="shared" ref="G5:G31" si="1">CEILING(SUM(D5:F5),0.5)</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>25011101003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1">
+        <f>_xlfn.XLOOKUP(B6,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E6" s="1">
+        <f>_xlfn.XLOOKUP(B6,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.75</v>
+      </c>
+      <c r="F6" s="1">
+        <f>_xlfn.XLOOKUP(B6,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>25011101004</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1">
+        <f>_xlfn.XLOOKUP(B7,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E7" s="1">
+        <f>_xlfn.XLOOKUP(B7,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F7" s="1">
+        <f>_xlfn.XLOOKUP(B7,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>25011101005</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1">
+        <f>_xlfn.XLOOKUP(B8,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E8" s="1">
+        <f>_xlfn.XLOOKUP(B8,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="1">
+        <f>_xlfn.XLOOKUP(B8,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>25011101008</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1">
+        <f>_xlfn.XLOOKUP(B9,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E9" s="1">
+        <f>_xlfn.XLOOKUP(B9,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F9" s="1">
+        <f>_xlfn.XLOOKUP(B9,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="15">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>25011101009</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
+        <f>_xlfn.XLOOKUP(B10,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <f>_xlfn.XLOOKUP(B10,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <f>_xlfn.XLOOKUP(B10,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>25011101010</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1">
+        <f>_xlfn.XLOOKUP(B11,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E11" s="1">
+        <f>_xlfn.XLOOKUP(B11,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F11" s="1">
+        <f>_xlfn.XLOOKUP(B11,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="15">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>25011101011</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1">
+        <f>_xlfn.XLOOKUP(B12,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <f>_xlfn.XLOOKUP(B12,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F12" s="1">
+        <f>_xlfn.XLOOKUP(B12,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="1"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>25011101012</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1">
+        <f>_xlfn.XLOOKUP(B13,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>6</v>
+      </c>
+      <c r="E13" s="1">
+        <f>_xlfn.XLOOKUP(B13,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F13" s="1">
+        <f>_xlfn.XLOOKUP(B13,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>25011101013</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1">
+        <f>_xlfn.XLOOKUP(B14,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>6</v>
+      </c>
+      <c r="E14" s="1">
+        <f>_xlfn.XLOOKUP(B14,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F14" s="1">
+        <f>_xlfn.XLOOKUP(B14,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>25011101014</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1">
+        <f>_xlfn.XLOOKUP(B15,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <f>_xlfn.XLOOKUP(B15,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F15" s="1">
+        <f>_xlfn.XLOOKUP(B15,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="15">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>25011101015</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1">
+        <f>_xlfn.XLOOKUP(B16,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E16" s="1">
+        <f>_xlfn.XLOOKUP(B16,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F16" s="1">
+        <f>_xlfn.XLOOKUP(B16,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="15">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>25011101016</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1">
+        <f>_xlfn.XLOOKUP(B17,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E17" s="1">
+        <f>_xlfn.XLOOKUP(B17,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3</v>
+      </c>
+      <c r="F17" s="1">
+        <f>_xlfn.XLOOKUP(B17,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="15">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>25011101017</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1">
+        <f>_xlfn.XLOOKUP(B18,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <f>_xlfn.XLOOKUP(B18,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F18" s="1">
+        <f>_xlfn.XLOOKUP(B18,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="15">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>25011101018</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1">
+        <f>_xlfn.XLOOKUP(B19,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <f>_xlfn.XLOOKUP(B19,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>1.875</v>
+      </c>
+      <c r="F19" s="1">
+        <f>_xlfn.XLOOKUP(B19,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="15">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>25011101019</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1">
+        <f>_xlfn.XLOOKUP(B20,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E20" s="1">
+        <f>_xlfn.XLOOKUP(B20,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F20" s="1">
+        <f>_xlfn.XLOOKUP(B20,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>25011101020</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1">
+        <f>_xlfn.XLOOKUP(B21,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E21" s="1">
+        <f>_xlfn.XLOOKUP(B21,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F21" s="1">
+        <f>_xlfn.XLOOKUP(B21,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="15">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>25011101021</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="1">
+        <f>_xlfn.XLOOKUP(B22,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E22" s="1">
+        <f>_xlfn.XLOOKUP(B22,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F22" s="1">
+        <f>_xlfn.XLOOKUP(B22,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="15">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>25011101022</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1">
+        <f>_xlfn.XLOOKUP(B23,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E23" s="1">
+        <f>_xlfn.XLOOKUP(B23,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.75</v>
+      </c>
+      <c r="F23" s="1">
+        <f>_xlfn.XLOOKUP(B23,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="15">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>25011101023</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="1">
+        <f>_xlfn.XLOOKUP(B24,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E24" s="1">
+        <f>_xlfn.XLOOKUP(B24,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F24" s="1">
+        <f>_xlfn.XLOOKUP(B24,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="15">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>25011101024</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="1">
+        <f>_xlfn.XLOOKUP(B25,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>6</v>
+      </c>
+      <c r="E25" s="1">
+        <f>_xlfn.XLOOKUP(B25,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F25" s="1">
+        <f>_xlfn.XLOOKUP(B25,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="15">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25011101025</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="1">
+        <f>_xlfn.XLOOKUP(B26,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="1">
+        <f>_xlfn.XLOOKUP(B26,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <f>_xlfn.XLOOKUP(B26,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>25011101026</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="1">
+        <f>_xlfn.XLOOKUP(B27,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E27" s="1">
+        <f>_xlfn.XLOOKUP(B27,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>1.875</v>
+      </c>
+      <c r="F27" s="1">
+        <f>_xlfn.XLOOKUP(B27,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="15">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>25011101027</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="1">
+        <f>_xlfn.XLOOKUP(B28,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E28" s="1">
+        <f>_xlfn.XLOOKUP(B28,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F28" s="1">
+        <f>_xlfn.XLOOKUP(B28,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="15">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>25011101028</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="1">
+        <f>_xlfn.XLOOKUP(B29,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>6</v>
+      </c>
+      <c r="E29" s="1">
+        <f>_xlfn.XLOOKUP(B29,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>2.25</v>
+      </c>
+      <c r="F29" s="1">
+        <f>_xlfn.XLOOKUP(B29,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="15">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>25011101029</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="1">
+        <f>_xlfn.XLOOKUP(B30,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E30" s="1">
+        <f>_xlfn.XLOOKUP(B30,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>3.75</v>
+      </c>
+      <c r="F30" s="1">
+        <f>_xlfn.XLOOKUP(B30,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="15">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>25011101030</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="1">
+        <f>_xlfn.XLOOKUP(B31,'TME 2-1 Attendance'!$B$4:$B$31,'TME 2-1 Attendance'!$E$4:$E$31)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="1">
+        <f>_xlfn.XLOOKUP(B31,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
+        <v>2.25</v>
+      </c>
+      <c r="F31" s="1">
+        <f>_xlfn.XLOOKUP(B31,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="15">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="5">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="F1:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/TME 2-1/Regular Assessment TME 2-1.xlsx
+++ b/TME 2-1/Regular Assessment TME 2-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\TME 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27A1D6A-4B11-4B58-B7BA-4A38E600C04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CFEDB2-E855-43E2-AF51-6D8869AD3C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TME 2-1 Attendance" sheetId="2" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="60">
   <si>
     <t>SL</t>
   </si>
@@ -217,21 +217,12 @@
     <t>Drew 2 Figures</t>
   </si>
   <si>
-    <t>Drew 3 Figures, Omit some actions</t>
-  </si>
-  <si>
-    <t>Drawing Not Clear</t>
-  </si>
-  <si>
     <t>NOAS</t>
   </si>
   <si>
     <t>NOC</t>
   </si>
   <si>
-    <t>Tuck, Miss</t>
-  </si>
-  <si>
     <t>BOEV</t>
   </si>
   <si>
@@ -245,6 +236,15 @@
   </si>
   <si>
     <t>Assignment 2</t>
+  </si>
+  <si>
+    <t>Not Submitted</t>
+  </si>
+  <si>
+    <t>Tuck, Miss Loop</t>
+  </si>
+  <si>
+    <t>Drawing Not Accurate &amp; Clear</t>
   </si>
 </sst>
 </file>
@@ -310,7 +310,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,6 +376,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD0CF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -431,7 +437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -476,6 +482,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -860,10 +869,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
@@ -894,7 +903,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
@@ -2581,6 +2590,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A66B3EF-818E-4A70-9374-2DAEC6B795EE}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2591,15 +2603,16 @@
     <col min="5" max="5" width="21.77734375" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.77734375" style="2" customWidth="1"/>
     <col min="7" max="7" width="9.21875" style="2" customWidth="1"/>
-    <col min="8" max="9" width="52.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
@@ -2607,16 +2620,16 @@
         <v>38</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="17" t="s">
+      <c r="G1" s="17"/>
+      <c r="H1" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2629,18 +2642,18 @@
         <v>28</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
+        <v>58</v>
+      </c>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
     </row>
     <row r="3" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -2659,13 +2672,13 @@
         <v>41</v>
       </c>
       <c r="F3" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G3" s="3">
         <v>7.5</v>
       </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
@@ -2680,14 +2693,16 @@
       <c r="D4" s="1">
         <v>7.5</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1">
+        <v>7</v>
+      </c>
       <c r="F4" s="1">
         <f t="shared" ref="F4:F31" si="0">SUM(D4:E4)</f>
-        <v>7.5</v>
+        <v>14.5</v>
       </c>
       <c r="G4" s="1">
         <f>F4/2</f>
-        <v>3.75</v>
+        <v>7.25</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -2706,14 +2721,16 @@
       <c r="D5" s="1">
         <v>7.5</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1">
+        <v>7.5</v>
+      </c>
       <c r="F5" s="1">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" ref="G5:G31" si="2">F5/2</f>
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -2732,14 +2749,16 @@
       <c r="D6" s="1">
         <v>7.5</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1">
+        <v>7.5</v>
+      </c>
       <c r="F6" s="1">
         <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="2"/>
         <v>7.5</v>
-      </c>
-      <c r="G6" s="1">
-        <f t="shared" si="2"/>
-        <v>3.75</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -2758,14 +2777,16 @@
       <c r="D7" s="1">
         <v>7</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="1">
+        <v>7</v>
+      </c>
       <c r="F7" s="1">
         <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="2"/>
         <v>7</v>
-      </c>
-      <c r="G7" s="1">
-        <f t="shared" si="2"/>
-        <v>3.5</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -2784,16 +2805,18 @@
       <c r="D8" s="1">
         <v>5</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F8" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="2"/>
-        <v>2.5</v>
-      </c>
-      <c r="H8" s="1" t="s">
+        <v>5.75</v>
+      </c>
+      <c r="H8" s="15" t="s">
         <v>48</v>
       </c>
       <c r="I8" s="1"/>
@@ -2812,14 +2835,16 @@
       <c r="D9" s="1">
         <v>6.5</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F9" s="1">
         <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="2"/>
         <v>6.5</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" si="2"/>
-        <v>3.25</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -2836,7 +2861,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="12"/>
-      <c r="E10" s="1"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2845,8 +2870,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="H10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
@@ -2862,14 +2891,16 @@
       <c r="D11" s="1">
         <v>7</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F11" s="1">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="2"/>
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2888,14 +2919,16 @@
       <c r="D12" s="1">
         <v>6.5</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F12" s="1">
         <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="2"/>
         <v>6.5</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="2"/>
-        <v>3.25</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2914,14 +2947,16 @@
       <c r="D13" s="1">
         <v>7</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1">
+        <v>7</v>
+      </c>
       <c r="F13" s="1">
         <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="2"/>
         <v>7</v>
-      </c>
-      <c r="G13" s="1">
-        <f t="shared" si="2"/>
-        <v>3.5</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2940,14 +2975,16 @@
       <c r="D14" s="1">
         <v>7</v>
       </c>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1">
+        <v>7</v>
+      </c>
       <c r="F14" s="1">
         <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="2"/>
         <v>7</v>
-      </c>
-      <c r="G14" s="1">
-        <f t="shared" si="2"/>
-        <v>3.5</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -2966,16 +3003,18 @@
       <c r="D15" s="1">
         <v>5.5</v>
       </c>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F15" s="1">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="2"/>
-        <v>2.75</v>
-      </c>
-      <c r="H15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="15" t="s">
         <v>42</v>
       </c>
       <c r="I15" s="1"/>
@@ -2992,17 +3031,20 @@
         <v>15</v>
       </c>
       <c r="D16" s="1">
-        <v>5</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="E16" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F16" s="1">
-        <v>5.5</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="2"/>
-        <v>2.75</v>
-      </c>
-      <c r="H16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15" t="s">
         <v>47</v>
       </c>
       <c r="I16" s="1"/>
@@ -3021,14 +3063,16 @@
       <c r="D17" s="1">
         <v>6</v>
       </c>
-      <c r="E17" s="1"/>
+      <c r="E17" s="1">
+        <v>7.5</v>
+      </c>
       <c r="F17" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -3047,19 +3091,23 @@
       <c r="D18" s="1">
         <v>5.5</v>
       </c>
-      <c r="E18" s="1"/>
+      <c r="E18" s="1">
+        <v>5</v>
+      </c>
       <c r="F18" s="1">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="2"/>
-        <v>2.75</v>
-      </c>
-      <c r="H18" s="1" t="s">
+        <v>5.25</v>
+      </c>
+      <c r="H18" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="15" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
@@ -3075,16 +3123,18 @@
       <c r="D19" s="1">
         <v>3.75</v>
       </c>
-      <c r="E19" s="1"/>
+      <c r="E19" s="1">
+        <v>5.5</v>
+      </c>
       <c r="F19" s="1">
         <f t="shared" si="0"/>
-        <v>3.75</v>
+        <v>9.25</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" si="2"/>
-        <v>1.875</v>
-      </c>
-      <c r="H19" s="1" t="s">
+        <v>4.625</v>
+      </c>
+      <c r="H19" s="15" t="s">
         <v>49</v>
       </c>
       <c r="I19" s="1"/>
@@ -3103,14 +3153,16 @@
       <c r="D20" s="1">
         <v>6.5</v>
       </c>
-      <c r="E20" s="1"/>
+      <c r="E20" s="1">
+        <v>7</v>
+      </c>
       <c r="F20" s="1">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>13.5</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" si="2"/>
-        <v>3.25</v>
+        <v>6.75</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -3129,16 +3181,18 @@
       <c r="D21" s="1">
         <v>5.5</v>
       </c>
-      <c r="E21" s="1"/>
+      <c r="E21" s="1">
+        <v>7</v>
+      </c>
       <c r="F21" s="1">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" si="2"/>
-        <v>2.75</v>
-      </c>
-      <c r="H21" s="1" t="s">
+        <v>6.25</v>
+      </c>
+      <c r="H21" s="15" t="s">
         <v>42</v>
       </c>
       <c r="I21" s="1"/>
@@ -3157,16 +3211,18 @@
       <c r="D22" s="1">
         <v>5.5</v>
       </c>
-      <c r="E22" s="1"/>
+      <c r="E22" s="1">
+        <v>7.5</v>
+      </c>
       <c r="F22" s="1">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" si="2"/>
-        <v>2.75</v>
-      </c>
-      <c r="H22" s="1" t="s">
+        <v>6.5</v>
+      </c>
+      <c r="H22" s="15" t="s">
         <v>42</v>
       </c>
       <c r="I22" s="1"/>
@@ -3183,16 +3239,18 @@
         <v>22</v>
       </c>
       <c r="D23" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="E23" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F23" s="1">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" si="2"/>
-        <v>3.75</v>
+        <v>6.75</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -3211,14 +3269,16 @@
       <c r="D24" s="1">
         <v>6.5</v>
       </c>
-      <c r="E24" s="1"/>
+      <c r="E24" s="1">
+        <v>6.5</v>
+      </c>
       <c r="F24" s="1">
         <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G24" s="1">
+        <f t="shared" si="2"/>
         <v>6.5</v>
-      </c>
-      <c r="G24" s="1">
-        <f t="shared" si="2"/>
-        <v>3.25</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -3237,19 +3297,23 @@
       <c r="D25" s="1">
         <v>5</v>
       </c>
-      <c r="E25" s="1"/>
+      <c r="E25" s="1">
+        <v>5.5</v>
+      </c>
       <c r="F25" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" si="2"/>
-        <v>2.5</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I25" s="1"/>
+        <v>5.25</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
@@ -3263,16 +3327,20 @@
         <v>25</v>
       </c>
       <c r="D26" s="12"/>
-      <c r="E26" s="1"/>
+      <c r="E26" s="1">
+        <v>7</v>
+      </c>
       <c r="F26" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -3289,19 +3357,23 @@
       <c r="D27" s="1">
         <v>3.75</v>
       </c>
-      <c r="E27" s="1"/>
+      <c r="E27" s="1">
+        <v>5.5</v>
+      </c>
       <c r="F27" s="1">
         <f t="shared" si="0"/>
-        <v>3.75</v>
+        <v>9.25</v>
       </c>
       <c r="G27" s="1">
         <f t="shared" si="2"/>
-        <v>1.875</v>
-      </c>
-      <c r="H27" s="1" t="s">
+        <v>4.625</v>
+      </c>
+      <c r="H27" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="I27" s="1"/>
+      <c r="I27" s="15" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
@@ -3317,14 +3389,16 @@
       <c r="D28" s="1">
         <v>6.5</v>
       </c>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1">
+        <v>7.5</v>
+      </c>
       <c r="F28" s="1">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>14</v>
       </c>
       <c r="G28" s="1">
         <f t="shared" si="2"/>
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -3343,17 +3417,19 @@
       <c r="D29" s="1">
         <v>4.5</v>
       </c>
-      <c r="E29" s="1"/>
+      <c r="E29" s="1">
+        <v>6</v>
+      </c>
       <c r="F29" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="G29" s="1">
         <f t="shared" si="2"/>
-        <v>2.25</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>51</v>
+        <v>5.25</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="I29" s="1"/>
     </row>
@@ -3371,14 +3447,16 @@
       <c r="D30" s="1">
         <v>7.5</v>
       </c>
-      <c r="E30" s="1"/>
+      <c r="E30" s="1">
+        <v>7.5</v>
+      </c>
       <c r="F30" s="1">
         <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G30" s="1">
+        <f t="shared" si="2"/>
         <v>7.5</v>
-      </c>
-      <c r="G30" s="1">
-        <f t="shared" si="2"/>
-        <v>3.75</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -3397,17 +3475,19 @@
       <c r="D31" s="1">
         <v>4.5</v>
       </c>
-      <c r="E31" s="1"/>
+      <c r="E31" s="1">
+        <v>7</v>
+      </c>
       <c r="F31" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="2"/>
-        <v>2.25</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>51</v>
+        <v>5.75</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="I31" s="1"/>
     </row>
@@ -3419,8 +3499,9 @@
     <mergeCell ref="H1:H3"/>
     <mergeCell ref="I1:I3"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="D3:E3" numberStoredAsText="1"/>
   </ignoredErrors>
@@ -3440,10 +3521,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
@@ -3461,7 +3542,7 @@
         <v>36</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3853,6 +3934,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C159D0FE-8346-4F75-A74F-7071A40E2D26}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3867,23 +3951,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="17"/>
       <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="20">
+      <c r="D1" s="21">
         <v>7.5</v>
       </c>
-      <c r="E1" s="20">
+      <c r="E1" s="21">
         <v>7.5</v>
       </c>
-      <c r="F1" s="20">
+      <c r="F1" s="21">
         <v>15</v>
       </c>
-      <c r="G1" s="18">
+      <c r="G1" s="19">
         <v>30</v>
       </c>
     </row>
@@ -3896,12 +3980,12 @@
         <v>28</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="19"/>
+        <v>52</v>
+      </c>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -3914,13 +3998,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>40</v>
@@ -3942,7 +4026,7 @@
       </c>
       <c r="E4" s="1">
         <f>_xlfn.XLOOKUP(B4,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.75</v>
+        <v>7.25</v>
       </c>
       <c r="F4" s="1">
         <f>_xlfn.XLOOKUP(B4,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -3950,7 +4034,7 @@
       </c>
       <c r="G4" s="15">
         <f>CEILING(SUM(D4:F4),0.5)</f>
-        <v>11.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3970,7 +4054,7 @@
       </c>
       <c r="E5" s="1">
         <f>_xlfn.XLOOKUP(B5,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="F5" s="1">
         <f>_xlfn.XLOOKUP(B5,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -3978,7 +4062,7 @@
       </c>
       <c r="G5" s="15">
         <f t="shared" ref="G5:G31" si="1">CEILING(SUM(D5:F5),0.5)</f>
-        <v>11.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3998,7 +4082,7 @@
       </c>
       <c r="E6" s="1">
         <f>_xlfn.XLOOKUP(B6,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="F6" s="1">
         <f>_xlfn.XLOOKUP(B6,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4006,7 +4090,7 @@
       </c>
       <c r="G6" s="15">
         <f t="shared" si="1"/>
-        <v>11.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -4026,7 +4110,7 @@
       </c>
       <c r="E7" s="1">
         <f>_xlfn.XLOOKUP(B7,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1">
         <f>_xlfn.XLOOKUP(B7,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4034,7 +4118,7 @@
       </c>
       <c r="G7" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -4054,7 +4138,7 @@
       </c>
       <c r="E8" s="1">
         <f>_xlfn.XLOOKUP(B8,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="F8" s="1">
         <f>_xlfn.XLOOKUP(B8,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4062,7 +4146,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -4082,7 +4166,7 @@
       </c>
       <c r="E9" s="1">
         <f>_xlfn.XLOOKUP(B9,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="F9" s="1">
         <f>_xlfn.XLOOKUP(B9,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4090,7 +4174,7 @@
       </c>
       <c r="G9" s="15">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -4138,7 +4222,7 @@
       </c>
       <c r="E11" s="1">
         <f>_xlfn.XLOOKUP(B11,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="F11" s="1">
         <f>_xlfn.XLOOKUP(B11,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4146,7 +4230,7 @@
       </c>
       <c r="G11" s="15">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -4166,7 +4250,7 @@
       </c>
       <c r="E12" s="1">
         <f>_xlfn.XLOOKUP(B12,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="F12" s="1">
         <f>_xlfn.XLOOKUP(B12,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4174,7 +4258,7 @@
       </c>
       <c r="G12" s="15">
         <f t="shared" si="1"/>
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -4194,7 +4278,7 @@
       </c>
       <c r="E13" s="1">
         <f>_xlfn.XLOOKUP(B13,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1">
         <f>_xlfn.XLOOKUP(B13,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4202,7 +4286,7 @@
       </c>
       <c r="G13" s="15">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -4222,7 +4306,7 @@
       </c>
       <c r="E14" s="1">
         <f>_xlfn.XLOOKUP(B14,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1">
         <f>_xlfn.XLOOKUP(B14,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4230,7 +4314,7 @@
       </c>
       <c r="G14" s="15">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -4250,7 +4334,7 @@
       </c>
       <c r="E15" s="1">
         <f>_xlfn.XLOOKUP(B15,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="F15" s="1">
         <f>_xlfn.XLOOKUP(B15,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4258,7 +4342,7 @@
       </c>
       <c r="G15" s="15">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -4278,7 +4362,7 @@
       </c>
       <c r="E16" s="1">
         <f>_xlfn.XLOOKUP(B16,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="F16" s="1">
         <f>_xlfn.XLOOKUP(B16,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4286,7 +4370,7 @@
       </c>
       <c r="G16" s="15">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -4306,7 +4390,7 @@
       </c>
       <c r="E17" s="1">
         <f>_xlfn.XLOOKUP(B17,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="F17" s="1">
         <f>_xlfn.XLOOKUP(B17,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4314,7 +4398,7 @@
       </c>
       <c r="G17" s="15">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -4334,7 +4418,7 @@
       </c>
       <c r="E18" s="1">
         <f>_xlfn.XLOOKUP(B18,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>2.75</v>
+        <v>5.25</v>
       </c>
       <c r="F18" s="1">
         <f>_xlfn.XLOOKUP(B18,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4342,7 +4426,7 @@
       </c>
       <c r="G18" s="15">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -4362,7 +4446,7 @@
       </c>
       <c r="E19" s="1">
         <f>_xlfn.XLOOKUP(B19,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>1.875</v>
+        <v>4.625</v>
       </c>
       <c r="F19" s="1">
         <f>_xlfn.XLOOKUP(B19,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4370,7 +4454,7 @@
       </c>
       <c r="G19" s="15">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -4390,7 +4474,7 @@
       </c>
       <c r="E20" s="1">
         <f>_xlfn.XLOOKUP(B20,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.25</v>
+        <v>6.75</v>
       </c>
       <c r="F20" s="1">
         <f>_xlfn.XLOOKUP(B20,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4398,7 +4482,7 @@
       </c>
       <c r="G20" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -4418,7 +4502,7 @@
       </c>
       <c r="E21" s="1">
         <f>_xlfn.XLOOKUP(B21,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>2.75</v>
+        <v>6.25</v>
       </c>
       <c r="F21" s="1">
         <f>_xlfn.XLOOKUP(B21,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4426,7 +4510,7 @@
       </c>
       <c r="G21" s="15">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -4446,7 +4530,7 @@
       </c>
       <c r="E22" s="1">
         <f>_xlfn.XLOOKUP(B22,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="F22" s="1">
         <f>_xlfn.XLOOKUP(B22,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4454,7 +4538,7 @@
       </c>
       <c r="G22" s="15">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -4474,7 +4558,7 @@
       </c>
       <c r="E23" s="1">
         <f>_xlfn.XLOOKUP(B23,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.75</v>
+        <v>6.75</v>
       </c>
       <c r="F23" s="1">
         <f>_xlfn.XLOOKUP(B23,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4482,7 +4566,7 @@
       </c>
       <c r="G23" s="15">
         <f t="shared" si="1"/>
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -4502,7 +4586,7 @@
       </c>
       <c r="E24" s="1">
         <f>_xlfn.XLOOKUP(B24,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="F24" s="1">
         <f>_xlfn.XLOOKUP(B24,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4510,7 +4594,7 @@
       </c>
       <c r="G24" s="15">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -4530,7 +4614,7 @@
       </c>
       <c r="E25" s="1">
         <f>_xlfn.XLOOKUP(B25,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="F25" s="1">
         <f>_xlfn.XLOOKUP(B25,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4538,7 +4622,7 @@
       </c>
       <c r="G25" s="15">
         <f t="shared" si="1"/>
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -4558,7 +4642,7 @@
       </c>
       <c r="E26" s="1">
         <f>_xlfn.XLOOKUP(B26,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="F26" s="1">
         <f>_xlfn.XLOOKUP(B26,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4566,7 +4650,7 @@
       </c>
       <c r="G26" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -4586,7 +4670,7 @@
       </c>
       <c r="E27" s="1">
         <f>_xlfn.XLOOKUP(B27,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>1.875</v>
+        <v>4.625</v>
       </c>
       <c r="F27" s="1">
         <f>_xlfn.XLOOKUP(B27,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4594,7 +4678,7 @@
       </c>
       <c r="G27" s="15">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -4614,7 +4698,7 @@
       </c>
       <c r="E28" s="1">
         <f>_xlfn.XLOOKUP(B28,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="F28" s="1">
         <f>_xlfn.XLOOKUP(B28,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4622,7 +4706,7 @@
       </c>
       <c r="G28" s="15">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -4642,7 +4726,7 @@
       </c>
       <c r="E29" s="1">
         <f>_xlfn.XLOOKUP(B29,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>2.25</v>
+        <v>5.25</v>
       </c>
       <c r="F29" s="1">
         <f>_xlfn.XLOOKUP(B29,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4650,7 +4734,7 @@
       </c>
       <c r="G29" s="15">
         <f t="shared" si="1"/>
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -4670,7 +4754,7 @@
       </c>
       <c r="E30" s="1">
         <f>_xlfn.XLOOKUP(B30,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="F30" s="1">
         <f>_xlfn.XLOOKUP(B30,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4678,7 +4762,7 @@
       </c>
       <c r="G30" s="15">
         <f t="shared" si="1"/>
-        <v>11.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -4698,7 +4782,7 @@
       </c>
       <c r="E31" s="1">
         <f>_xlfn.XLOOKUP(B31,Assignment!$B$4:$B$31,Assignment!$G$4:$G$31)</f>
-        <v>2.25</v>
+        <v>5.75</v>
       </c>
       <c r="F31" s="1">
         <f>_xlfn.XLOOKUP(B31,'Class Test'!$B$4:$B$31,'Class Test'!$D$4:$D$31)</f>
@@ -4706,7 +4790,7 @@
       </c>
       <c r="G31" s="15">
         <f t="shared" si="1"/>
-        <v>2.5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4718,7 +4802,8 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="F1:F2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="87" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>